--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>核对周期</t>
   </si>
@@ -167,9 +167,6 @@
   </si>
   <si>
     <t>{.soCode}</t>
-  </si>
-  <si>
-    <t>{.outstockCode}</t>
   </si>
   <si>
     <t>{.skuQty}</t>
@@ -1169,7 +1166,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AE2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="30.625" customWidth="1"/>
@@ -1191,17 +1188,17 @@
     <col min="18" max="18" width="18.25" customWidth="1"/>
     <col min="19" max="19" width="11.5" customWidth="1"/>
     <col min="20" max="20" width="10.375" customWidth="1"/>
-    <col min="21" max="22" width="14.875" customWidth="1"/>
-    <col min="23" max="23" width="12.125" customWidth="1"/>
-    <col min="24" max="24" width="12.625" customWidth="1"/>
-    <col min="25" max="25" width="14.875" customWidth="1"/>
-    <col min="26" max="26" width="11.5" customWidth="1"/>
-    <col min="27" max="27" width="10.375" customWidth="1"/>
-    <col min="28" max="28" width="14.875" customWidth="1"/>
-    <col min="30" max="30" width="10.375" customWidth="1"/>
+    <col min="21" max="21" width="14.875" customWidth="1"/>
+    <col min="22" max="22" width="12.125" customWidth="1"/>
+    <col min="23" max="23" width="12.625" customWidth="1"/>
+    <col min="24" max="24" width="14.875" customWidth="1"/>
+    <col min="25" max="25" width="11.5" customWidth="1"/>
+    <col min="26" max="26" width="10.375" customWidth="1"/>
+    <col min="27" max="27" width="14.875" customWidth="1"/>
+    <col min="29" max="29" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:32">
+    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1262,44 +1259,41 @@
       <c r="T1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>8</v>
+      <c r="U1" t="s">
+        <v>16</v>
       </c>
       <c r="V1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W1" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="X1" t="s">
+        <v>18</v>
+      </c>
       <c r="Y1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="AA1" t="s">
+        <v>21</v>
+      </c>
       <c r="AB1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AC1" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="AD1" t="s">
+        <v>24</v>
+      </c>
       <c r="AE1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:32">
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1392,9 +1386,6 @@
       </c>
       <c r="AE2" t="s">
         <v>56</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>核对周期</t>
   </si>
@@ -58,10 +58,16 @@
     <t>出库单号</t>
   </si>
   <si>
-    <t>库存SKU*数量</t>
-  </si>
-  <si>
-    <t>ERPSKU*数量</t>
+    <t>库存SKU</t>
+  </si>
+  <si>
+    <t>库存SKU数量</t>
+  </si>
+  <si>
+    <t>ERPSKU</t>
+  </si>
+  <si>
+    <t>ERPSKU数量</t>
   </si>
   <si>
     <t>出库仓库</t>
@@ -136,10 +142,16 @@
     <t>{.platformOutstockCode}</t>
   </si>
   <si>
-    <t>{.stockSkuQty}</t>
-  </si>
-  <si>
-    <t>{.platformSkuQty}</t>
+    <t>{.stockSku}</t>
+  </si>
+  <si>
+    <t>{.stockQty}</t>
+  </si>
+  <si>
+    <t>{.platformSkuNo}</t>
+  </si>
+  <si>
+    <t>{.platformQty}</t>
   </si>
   <si>
     <t>{.platformWarehouseName}</t>
@@ -1166,7 +1178,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE2"/>
+  <dimension ref="A1:AG2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="30.625" customWidth="1"/>
@@ -1178,27 +1190,27 @@
     <col min="8" max="8" width="22.625" customWidth="1"/>
     <col min="9" max="9" width="15.25" customWidth="1"/>
     <col min="10" max="10" width="20.375" customWidth="1"/>
-    <col min="11" max="11" width="13.75" customWidth="1"/>
-    <col min="12" max="12" width="14.875" customWidth="1"/>
-    <col min="13" max="13" width="19.375" customWidth="1"/>
-    <col min="14" max="14" width="14.875" customWidth="1"/>
+    <col min="11" max="12" width="13.75" customWidth="1"/>
+    <col min="13" max="14" width="14.875" customWidth="1"/>
     <col min="15" max="15" width="19.375" customWidth="1"/>
     <col min="16" max="16" width="14.875" customWidth="1"/>
-    <col min="17" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="18.25" customWidth="1"/>
-    <col min="19" max="19" width="11.5" customWidth="1"/>
-    <col min="20" max="20" width="10.375" customWidth="1"/>
-    <col min="21" max="21" width="14.875" customWidth="1"/>
-    <col min="22" max="22" width="12.125" customWidth="1"/>
-    <col min="23" max="23" width="12.625" customWidth="1"/>
-    <col min="24" max="24" width="14.875" customWidth="1"/>
-    <col min="25" max="25" width="11.5" customWidth="1"/>
-    <col min="26" max="26" width="10.375" customWidth="1"/>
-    <col min="27" max="27" width="14.875" customWidth="1"/>
-    <col min="29" max="29" width="10.375" customWidth="1"/>
+    <col min="17" max="17" width="19.375" customWidth="1"/>
+    <col min="18" max="18" width="14.875" customWidth="1"/>
+    <col min="19" max="19" width="16" customWidth="1"/>
+    <col min="20" max="20" width="18.25" customWidth="1"/>
+    <col min="21" max="21" width="11.5" customWidth="1"/>
+    <col min="22" max="22" width="10.375" customWidth="1"/>
+    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="24" max="24" width="12.125" customWidth="1"/>
+    <col min="25" max="25" width="12.625" customWidth="1"/>
+    <col min="26" max="26" width="14.875" customWidth="1"/>
+    <col min="27" max="27" width="11.5" customWidth="1"/>
+    <col min="28" max="28" width="10.375" customWidth="1"/>
+    <col min="29" max="29" width="14.875" customWidth="1"/>
+    <col min="31" max="31" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:31">
+    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:33">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1241,151 +1253,163 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
       <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
         <v>3</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>5</v>
+      </c>
+      <c r="U1" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="W1" t="s">
+        <v>18</v>
+      </c>
+      <c r="X1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" t="s">
-        <v>5</v>
-      </c>
-      <c r="S1" t="s">
-        <v>6</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="U1" t="s">
-        <v>16</v>
-      </c>
-      <c r="V1" t="s">
-        <v>17</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="X1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" t="s">
         <v>20</v>
       </c>
       <c r="AA1" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" t="s">
         <v>23</v>
       </c>
       <c r="AD1" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AF1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:33">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="S2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="W2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="X2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="Z2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="AA2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="AB2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="AC2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AD2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AE2" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncExport.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
   <si>
     <t>核对周期</t>
   </si>
@@ -85,7 +85,10 @@
     <t>店铺</t>
   </si>
   <si>
-    <t>SKU*数量</t>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>数量</t>
   </si>
   <si>
     <t>ERP仓库名称</t>
@@ -181,7 +184,10 @@
     <t>{.soCode}</t>
   </si>
   <si>
-    <t>{.skuQty}</t>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
   </si>
   <si>
     <t>{.erpWarehouseName}</t>
@@ -1178,7 +1184,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AG2"/>
+  <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="30.625" customWidth="1"/>
@@ -1201,16 +1207,16 @@
     <col min="21" max="21" width="11.5" customWidth="1"/>
     <col min="22" max="22" width="10.375" customWidth="1"/>
     <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="24" max="24" width="12.125" customWidth="1"/>
-    <col min="25" max="25" width="12.625" customWidth="1"/>
-    <col min="26" max="26" width="14.875" customWidth="1"/>
-    <col min="27" max="27" width="11.5" customWidth="1"/>
-    <col min="28" max="28" width="10.375" customWidth="1"/>
-    <col min="29" max="29" width="14.875" customWidth="1"/>
-    <col min="31" max="31" width="10.375" customWidth="1"/>
+    <col min="24" max="25" width="12.125" customWidth="1"/>
+    <col min="26" max="26" width="12.625" customWidth="1"/>
+    <col min="27" max="27" width="14.875" customWidth="1"/>
+    <col min="28" max="28" width="11.5" customWidth="1"/>
+    <col min="29" max="29" width="10.375" customWidth="1"/>
+    <col min="30" max="30" width="14.875" customWidth="1"/>
+    <col min="32" max="32" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:33">
+    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:34">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1283,133 +1289,139 @@
       <c r="X1" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>20</v>
       </c>
       <c r="AA1" t="s">
         <v>21</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>23</v>
       </c>
       <c r="AD1" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>26</v>
       </c>
       <c r="AG1" t="s">
         <v>27</v>
       </c>
+      <c r="AH1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:33">
+    <row r="2" spans="1:34">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="V2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Y2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AC2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AD2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AE2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AF2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AG2" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/dmp/adsErpDiffOutstockSyncExport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="67">
   <si>
     <t>核对周期</t>
   </si>
@@ -58,6 +58,12 @@
     <t>出库单号</t>
   </si>
   <si>
+    <t>平台物流跟踪号</t>
+  </si>
+  <si>
+    <t>物流跟踪号</t>
+  </si>
+  <si>
     <t>库存SKU</t>
   </si>
   <si>
@@ -143,6 +149,12 @@
   </si>
   <si>
     <t>{.platformOutstockCode}</t>
+  </si>
+  <si>
+    <t>{.platformTrackNo}</t>
+  </si>
+  <si>
+    <t>{.trackNo}</t>
   </si>
   <si>
     <t>{.stockSku}</t>
@@ -1184,7 +1196,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AJ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="2" width="30.625" customWidth="1"/>
@@ -1195,28 +1207,30 @@
     <col min="7" max="7" width="15.5" customWidth="1"/>
     <col min="8" max="8" width="22.625" customWidth="1"/>
     <col min="9" max="9" width="15.25" customWidth="1"/>
-    <col min="10" max="10" width="20.375" customWidth="1"/>
-    <col min="11" max="12" width="13.75" customWidth="1"/>
-    <col min="13" max="14" width="14.875" customWidth="1"/>
-    <col min="15" max="15" width="19.375" customWidth="1"/>
-    <col min="16" max="16" width="14.875" customWidth="1"/>
+    <col min="10" max="10" width="19.5" customWidth="1"/>
+    <col min="11" max="11" width="20.625" customWidth="1"/>
+    <col min="12" max="12" width="20.375" customWidth="1"/>
+    <col min="13" max="14" width="13.75" customWidth="1"/>
+    <col min="15" max="16" width="14.875" customWidth="1"/>
     <col min="17" max="17" width="19.375" customWidth="1"/>
     <col min="18" max="18" width="14.875" customWidth="1"/>
-    <col min="19" max="19" width="16" customWidth="1"/>
-    <col min="20" max="20" width="18.25" customWidth="1"/>
-    <col min="21" max="21" width="11.5" customWidth="1"/>
-    <col min="22" max="22" width="10.375" customWidth="1"/>
-    <col min="23" max="23" width="14.875" customWidth="1"/>
-    <col min="24" max="25" width="12.125" customWidth="1"/>
-    <col min="26" max="26" width="12.625" customWidth="1"/>
-    <col min="27" max="27" width="14.875" customWidth="1"/>
-    <col min="28" max="28" width="11.5" customWidth="1"/>
-    <col min="29" max="29" width="10.375" customWidth="1"/>
-    <col min="30" max="30" width="14.875" customWidth="1"/>
-    <col min="32" max="32" width="10.375" customWidth="1"/>
+    <col min="19" max="19" width="19.375" customWidth="1"/>
+    <col min="20" max="20" width="14.875" customWidth="1"/>
+    <col min="21" max="21" width="16" customWidth="1"/>
+    <col min="22" max="22" width="18.25" customWidth="1"/>
+    <col min="23" max="23" width="11.5" customWidth="1"/>
+    <col min="24" max="24" width="10.375" customWidth="1"/>
+    <col min="25" max="25" width="14.875" customWidth="1"/>
+    <col min="26" max="27" width="12.125" customWidth="1"/>
+    <col min="28" max="28" width="12.625" customWidth="1"/>
+    <col min="29" max="29" width="14.875" customWidth="1"/>
+    <col min="30" max="30" width="11.5" customWidth="1"/>
+    <col min="31" max="31" width="10.375" customWidth="1"/>
+    <col min="32" max="32" width="14.875" customWidth="1"/>
+    <col min="34" max="34" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:34">
+    <row r="1" customFormat="1" ht="19" customHeight="1" spans="1:36">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1244,13 +1258,13 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -1265,163 +1279,175 @@
       <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
       <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
         <v>3</v>
       </c>
-      <c r="S1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" t="s">
         <v>5</v>
       </c>
-      <c r="U1" t="s">
+      <c r="W1" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="W1" t="s">
-        <v>18</v>
-      </c>
-      <c r="X1" t="s">
-        <v>19</v>
       </c>
       <c r="Y1" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>15</v>
+      <c r="Z1" t="s">
+        <v>21</v>
       </c>
       <c r="AA1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AB1" t="s">
         <v>22</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC1" t="s">
         <v>23</v>
       </c>
       <c r="AD1" t="s">
         <v>24</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" t="s">
         <v>26</v>
       </c>
       <c r="AG1" t="s">
         <v>27</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="AI1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="P2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="T2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="V2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="W2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Y2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Z2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="AA2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AB2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="AC2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AD2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="AE2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AF2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="AG2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="AH2" t="s">
-        <v>62</v>
+        <v>64</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
